--- a/TestKitDemo/TC01/Detail.xlsx
+++ b/TestKitDemo/TC01/Detail.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\TestKitDemo\TC01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\School\NET\auto-grading\TestKitDemo\TC01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7C4AEB-AD01-411C-B432-9A3721D59F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE96EE00-CC48-4F27-AE31-F1A5FBC0EDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3480" yWindow="3204" windowWidth="17268" windowHeight="9036" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="InputClients" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>Stage</t>
   </si>
@@ -69,10 +69,6 @@
     <t>ByteSize</t>
   </si>
   <si>
-    <t xml:space="preserve">Client started, connecting to Server at http://localhost:5000/
-Please enter integer number : </t>
-  </si>
-  <si>
     <t>GET</t>
   </si>
   <si>
@@ -89,9 +85,6 @@
   </si>
   <si>
     <t>DataTypeMiddleware</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Server started at http://localhost:5001/</t>
   </si>
   <si>
     <t>GET /books/1</t>
@@ -600,16 +593,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
@@ -618,22 +607,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -661,27 +650,23 @@
         <v>9</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
+      <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
@@ -690,19 +675,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/TestKitDemo/TC01/Detail.xlsx
+++ b/TestKitDemo/TC01/Detail.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\School\NET\auto-grading\TestKitDemo\TC01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\TestKitDemo\TC01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE96EE00-CC48-4F27-AE31-F1A5FBC0EDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05570B0D-AFE7-4071-A51F-05A5BC62FAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3480" yWindow="3204" windowWidth="17268" windowHeight="9036" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9036" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="InputClients" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>Stage</t>
   </si>
@@ -69,6 +69,10 @@
     <t>ByteSize</t>
   </si>
   <si>
+    <t xml:space="preserve">Client started, connecting to Server at http://localhost:5000/
+Please enter integer number : </t>
+  </si>
+  <si>
     <t>GET</t>
   </si>
   <si>
@@ -87,6 +91,9 @@
     <t>DataTypeMiddleware</t>
   </si>
   <si>
+    <t xml:space="preserve"> Server started at http://localhost:5001/</t>
+  </si>
+  <si>
     <t>GET /books/1</t>
   </si>
   <si>
@@ -94,6 +101,18 @@
   </si>
   <si>
     <t>0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  BookId: 1, 
+  Title: Harry Potter and the Philosopher's Stone, 
+  PublicationYear: 1997, 
+  GenreName: Fantasy
+  BookId: 3, 
+  Title: The Hobbit, 
+  PublicationYear: 1937, 
+  GenreName: Fantasy
+----------------------------------------
+Please enter integer number : </t>
   </si>
   <si>
     <t>[
@@ -110,18 +129,6 @@
     "GenreName": "Fantasy"
   }
 ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  BookId: 1, 
-  Title: Harry Potter and the Philosopher's Stone, 
-  PublicationYear: 1997, 
-  GenreName: Fantasy
-  BookId: 3, 
-  Title: The Hobbit, 
-  PublicationYear: 1937, 
-  GenreName: Fantasy
-----------------------------------------
-Please enter integer number : </t>
   </si>
 </sst>
 </file>
@@ -593,12 +600,16 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
+    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="E2" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
@@ -607,22 +618,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -650,23 +661,27 @@
         <v>9</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
@@ -675,19 +690,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/TestKitDemo/TC01/Detail.xlsx
+++ b/TestKitDemo/TC01/Detail.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\TestKitDemo\TC01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05570B0D-AFE7-4071-A51F-05A5BC62FAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10757E3B-8BDD-46C1-89FA-DBCDD8BE6F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9036" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="InputClients" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>Stage</t>
   </si>
@@ -69,10 +69,6 @@
     <t>ByteSize</t>
   </si>
   <si>
-    <t xml:space="preserve">Client started, connecting to Server at http://localhost:5000/
-Please enter integer number : </t>
-  </si>
-  <si>
     <t>GET</t>
   </si>
   <si>
@@ -89,9 +85,6 @@
   </si>
   <si>
     <t>DataTypeMiddleware</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Server started at http://localhost:5001/</t>
   </si>
   <si>
     <t>GET /books/1</t>
@@ -600,16 +593,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
@@ -618,22 +607,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -661,27 +650,23 @@
         <v>9</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
+      <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
@@ -690,19 +675,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
